--- a/public/assets/templates/Dwell-Central-template.xlsx
+++ b/public/assets/templates/Dwell-Central-template.xlsx
@@ -34,7 +34,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F3D4F"/>
+      <color rgb="00113263"/>
       <sz val="18"/>
     </font>
     <font>
@@ -42,7 +42,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F3D4F"/>
+      <color rgb="00113263"/>
       <sz val="12"/>
     </font>
     <font>
@@ -67,7 +67,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3D4F"/>
+        <fgColor rgb="00113263"/>
       </patternFill>
     </fill>
     <fill>
@@ -202,7 +202,7 @@
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Optional. Used in the org chart, like #1F3D4F.</t>
+        <t>Optional. Used in the org chart, like #113263.</t>
       </text>
     </comment>
   </commentList>
@@ -869,7 +869,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>#1F3D4F</t>
+          <t>#113263</t>
         </is>
       </c>
       <c r="C2" s="7" t="n"/>
